--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2025.xlsx
@@ -562,7 +562,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1708,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1899,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2147,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2212,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2277,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
